--- a/data/trans_orig/IQ2608_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2608_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47154</t>
+          <t>46933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60537</t>
+          <t>60399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>80734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60357</t>
+          <t>59611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42645</t>
+          <t>43127</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87170</t>
+          <t>87709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115372</t>
+          <t>116069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119869</t>
+          <t>121339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150452</t>
+          <t>151240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215135</t>
+          <t>216340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257767</t>
+          <t>258554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125103</t>
+          <t>126139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156918</t>
+          <t>156992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>133123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164063</t>
+          <t>164733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265996</t>
+          <t>268225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311809</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93025</t>
+          <t>93485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121599</t>
+          <t>121890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117422</t>
+          <t>118392</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148027</t>
+          <t>149586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>219938</t>
+          <t>218062</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>262510</t>
+          <t>259832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>32986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35554</t>
+          <t>35662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55241</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50168</t>
+          <t>50217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70630</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99673</t>
+          <t>97627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>39227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58148</t>
+          <t>57442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>48835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68035</t>
+          <t>68441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93449</t>
+          <t>92193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119533</t>
+          <t>119190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55656</t>
+          <t>55076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85822</t>
+          <t>84914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112050</t>
+          <t>111773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>41309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61800</t>
+          <t>61881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46782</t>
+          <t>47765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104067</t>
+          <t>103156</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162088</t>
+          <t>162843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199008</t>
+          <t>197897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212110</t>
+          <t>211930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252889</t>
+          <t>252188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>388249</t>
+          <t>385206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>441224</t>
+          <t>440903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203665</t>
+          <t>205280</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243026</t>
+          <t>243486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,47 +2907,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>36,63%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>216504</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>198290</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>238780</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>30,64%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>216504</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>195694</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>236845</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,64%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408653</t>
+          <t>411303</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>463509</t>
+          <t>467781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>157339</t>
+          <t>157900</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>192901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171283</t>
+          <t>170938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209991</t>
+          <t>206596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>340402</t>
+          <t>337121</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>391336</t>
+          <t>392521</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24789</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47583</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>78289</t>
+          <t>77881</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42265</t>
+          <t>42244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66706</t>
+          <t>65132</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>101538</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>136800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2012 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2012 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>59853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59684</t>
+          <t>59658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94283</t>
+          <t>94441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116895</t>
+          <t>115354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29409</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>47870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201862</t>
+          <t>201059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>236801</t>
+          <t>236741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>223696</t>
+          <t>224366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260242</t>
+          <t>260733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>437679</t>
+          <t>438528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>486972</t>
+          <t>488404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>112409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143466</t>
+          <t>142722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125290</t>
+          <t>124598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159526</t>
+          <t>156553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247939</t>
+          <t>244732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293864</t>
+          <t>292372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67910</t>
+          <t>66887</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47922</t>
+          <t>47541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71791</t>
+          <t>70916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99198</t>
+          <t>97990</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131873</t>
+          <t>131296</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16660</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36202</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74737</t>
+          <t>74707</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96002</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68420</t>
+          <t>68602</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90008</t>
+          <t>89931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148716</t>
+          <t>149319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179123</t>
+          <t>180611</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41178</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60357</t>
+          <t>61365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71840</t>
+          <t>73017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99902</t>
+          <t>99168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127842</t>
+          <t>127914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,82 +5297,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11261</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17379</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>25852</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>19204</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>34967</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11261</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6777</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17714</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>25852</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>18380</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>34061</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>337852</t>
+          <t>336594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>379282</t>
+          <t>380660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>351742</t>
+          <t>351512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>396220</t>
+          <t>396006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>700198</t>
+          <t>699557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>763840</t>
+          <t>765649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177821</t>
+          <t>180328</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>216773</t>
+          <t>219391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>199073</t>
+          <t>197997</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>240821</t>
+          <t>241144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>392816</t>
+          <t>390971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>449657</t>
+          <t>449286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>69200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96957</t>
+          <t>96414</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65861</t>
+          <t>64915</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>91361</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>141129</t>
+          <t>141189</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>181506</t>
+          <t>178406</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>27890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27312</t>
+          <t>26580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47573</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44514</t>
+          <t>43501</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44552</t>
+          <t>44644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>56097</t>
+          <t>57226</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83042</t>
+          <t>83498</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2016 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2016 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36952</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>26102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>39191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55161</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73526</t>
+          <t>72875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20699</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34269</t>
+          <t>34313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35247</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53399</t>
+          <t>54197</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>183292</t>
+          <t>180607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217555</t>
+          <t>216215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185563</t>
+          <t>185243</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220327</t>
+          <t>221426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375360</t>
+          <t>377152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>426772</t>
+          <t>425087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157991</t>
+          <t>158473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191749</t>
+          <t>192025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184613</t>
+          <t>184455</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220286</t>
+          <t>220448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352989</t>
+          <t>353058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>402220</t>
+          <t>402376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44154</t>
+          <t>42787</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>65166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92151</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123440</t>
+          <t>123407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>22838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>40779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29319</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41829</t>
+          <t>41106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65247</t>
+          <t>64215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>66095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86467</t>
+          <t>86637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70985</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92240</t>
+          <t>93690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>142680</t>
+          <t>142127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>172308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50100</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70465</t>
+          <t>70453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58039</t>
+          <t>56011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77935</t>
+          <t>77367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113246</t>
+          <t>113939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143138</t>
+          <t>143562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>28179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47871</t>
+          <t>46699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>34079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>283203</t>
+          <t>287298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>326179</t>
+          <t>329408</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>295362</t>
+          <t>294459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>338142</t>
+          <t>340337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595891</t>
+          <t>592177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>655535</t>
+          <t>652926</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233789</t>
+          <t>231566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>272305</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>275937</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>318816</t>
+          <t>320255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>522359</t>
+          <t>515062</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>582185</t>
+          <t>577152</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63751</t>
+          <t>63579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91060</t>
+          <t>89696</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92694</t>
+          <t>95700</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>136966</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174334</t>
+          <t>176754</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59757</t>
+          <t>59151</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48270</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>70316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99506</t>
+          <t>98680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si utilizan camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si el verano pasado utilizaron camiseta, gorra, gafas de sol o sombrero para protegerse del sol en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27937</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48375</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75883</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36894</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67638</t>
+          <t>67249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71222</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98299</t>
+          <t>98000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33581</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44564</t>
+          <t>44422</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>49059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73172</t>
+          <t>71825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7508</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25541</t>
+          <t>25647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44535</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26220</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,82 +11328,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>4227</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>9082</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6311</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>9313</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>419</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30965</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>41807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64163</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78527</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>107889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>94927</t>
+          <t>93658</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117338</t>
+          <t>117440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>152351</t>
+          <t>151772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37694</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60235</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>70643</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
